--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trddepovaluationduration/TrdDepoValuationDuration001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trddepovaluationduration/TrdDepoValuationDuration001.xlsx
@@ -58,10 +58,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计划支付日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>实际支付日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,6 +67,10 @@
   </si>
   <si>
     <t>实收本金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计息结束日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -493,16 +493,16 @@
         <v>9</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>5</v>
